--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_312_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_312_R32.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3431</v>
+        <v>4.6657</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4695</v>
+        <v>3.5898</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8736</v>
+        <v>1.0759</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8575</v>
+        <v>2.8943</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0945</v>
+        <v>1.683</v>
       </c>
       <c r="I2" t="n">
-        <v>0.763</v>
+        <v>1.2113</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3366</v>
+        <v>3.4664</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6742</v>
+        <v>2.2519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6625</v>
+        <v>1.2146</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4791</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5796</v>
+        <v>-0.5688</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1005</v>
+        <v>-0.0033</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.232</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3258</v>
+        <v>-0.6203</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6869</v>
+        <v>-0.1808</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3611</v>
+        <v>-0.4395</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5142</v>
+        <v>4.1293</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4719</v>
+        <v>3.0541</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0423</v>
+        <v>1.0752</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8943</v>
+        <v>1.8575</v>
       </c>
       <c r="H3" t="n">
-        <v>1.683</v>
+        <v>1.0945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2113</v>
+        <v>0.763</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4664</v>
+        <v>2.3366</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2519</v>
+        <v>1.6742</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2146</v>
+        <v>0.6625</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.4791</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5688</v>
+        <v>-0.5796</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0033</v>
+        <v>0.1005</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7718</v>
+        <v>0.112</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2987</v>
+        <v>0.2715</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4731</v>
+        <v>-0.1595</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9311</v>
+        <v>3.9819</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4928</v>
+        <v>1.6108</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4383</v>
+        <v>2.3711</v>
       </c>
       <c r="G4" t="n">
         <v>1.92</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7723</v>
+        <v>-0.7215</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3242</v>
+        <v>-0.3914</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4913</v>
+        <v>3.3889</v>
       </c>
       <c r="E5" t="n">
-        <v>2.417</v>
+        <v>2.6844</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0742</v>
+        <v>0.7046</v>
       </c>
       <c r="G5" t="n">
         <v>3.8185</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.402</v>
+        <v>0.2996</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7468</v>
+        <v>-0.4795</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1488</v>
+        <v>0.7791</v>
       </c>
       <c r="V5" t="n">
         <v>2.2862</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8504</v>
+        <v>3.2185</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1848</v>
+        <v>2.4521</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6656</v>
+        <v>0.7664</v>
       </c>
       <c r="G6" t="n">
         <v>2.5617</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0593</v>
+        <v>0.4274</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5975</v>
+        <v>-0.3301</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9304</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8454</v>
+        <v>2.9969</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6541</v>
+        <v>1.772</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1913</v>
+        <v>1.2249</v>
       </c>
       <c r="G7" t="n">
         <v>3.0811</v>
@@ -1000,13 +1000,13 @@
         <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0038</v>
+        <v>-0.8522</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6304</v>
+        <v>-0.5968</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0228</v>
+        <v>2.694</v>
       </c>
       <c r="E8" t="n">
-        <v>2.134</v>
+        <v>2.6372</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1112</v>
+        <v>0.0569</v>
       </c>
       <c r="G8" t="n">
         <v>5.1506</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1041</v>
+        <v>0.7754</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5975</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7016</v>
+        <v>0.8696</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6083</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5235</v>
+        <v>1.7759</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1185</v>
+        <v>0.2365</v>
       </c>
       <c r="F9" t="n">
-        <v>1.405</v>
+        <v>1.5394</v>
       </c>
       <c r="G9" t="n">
         <v>2.5398</v>
@@ -1156,13 +1156,13 @@
         <v>2.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1606</v>
+        <v>-0.9082</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5632</v>
+        <v>-0.4288</v>
       </c>
       <c r="V9" t="n">
         <v>1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6156</v>
+        <v>-0.2116</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3318</v>
+        <v>-0.0959</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2838</v>
+        <v>-0.1158</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8077</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5759</v>
+        <v>-0.172</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1709</v>
+        <v>0.3389</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. RANDOLPH</t>
+          <t>K. EDWARDS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0559</v>
+        <v>-1.2536</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2523</v>
+        <v>1.1169</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8036</v>
+        <v>-2.3705</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1813</v>
+        <v>2.0332</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4357</v>
+        <v>-1.3228</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2544</v>
+        <v>3.356</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4412</v>
+        <v>2.6696</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6988</v>
+        <v>-0.9005</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2576</v>
+        <v>3.5701</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7401</v>
+        <v>-0.6364</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7369</v>
+        <v>-0.4223</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0033</v>
+        <v>-0.214</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.9994</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1889</v>
+        <v>-0.393</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4547</v>
+        <v>1.3924</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.214</v>
+        <v>-3.3584</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.214</v>
+        <v>-3.3584</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. EDWARDS</t>
+          <t>L. RANDOLPH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1183</v>
+        <v>-1.3447</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6137</v>
+        <v>-0.5747</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7319</v>
+        <v>-0.77</v>
       </c>
       <c r="G12" t="n">
-        <v>2.0332</v>
+        <v>-1.1813</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3228</v>
+        <v>-1.4357</v>
       </c>
       <c r="I12" t="n">
-        <v>3.356</v>
+        <v>0.2544</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6696</v>
+        <v>-0.4412</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9005</v>
+        <v>-0.6988</v>
       </c>
       <c r="L12" t="n">
-        <v>3.5701</v>
+        <v>0.2576</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6364</v>
+        <v>-0.7401</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4223</v>
+        <v>-0.7369</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.214</v>
+        <v>-0.0033</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1347</v>
+        <v>0.3547</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8962</v>
+        <v>-0.1336</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0309</v>
+        <v>0.4883</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.3584</v>
+        <v>-1.214</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.3584</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8764</v>
+        <v>-2.4388</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9378</v>
+        <v>-1.7019</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9386</v>
+        <v>-0.7369</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8694</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7029</v>
+        <v>-0.2653</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1801</v>
+        <v>0.0215</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5361</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.8556</v>
+        <v>21.6024</v>
       </c>
       <c r="E14" t="n">
-        <v>16.0344</v>
+        <v>16.7813</v>
       </c>
       <c r="F14" t="n">
-        <v>4.8212</v>
+        <v>4.821200000000001</v>
       </c>
       <c r="G14" t="n">
         <v>21.9983</v>
       </c>
       <c r="H14" t="n">
-        <v>7.292599999999998</v>
+        <v>7.2926</v>
       </c>
       <c r="I14" t="n">
         <v>14.7056</v>
@@ -1546,13 +1546,13 @@
         <v>17.3967</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3178</v>
+        <v>-0.571</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.9495</v>
+        <v>-3.2026</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6316</v>
+        <v>2.6314</v>
       </c>
       <c r="V14" t="n">
         <v>-2.1444</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1934</v>
+        <v>3.3243</v>
       </c>
       <c r="E15" t="n">
-        <v>2.744</v>
+        <v>5.7563</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4494</v>
+        <v>-2.4319</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9898</v>
+        <v>-3.2343</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2736</v>
+        <v>-0.4671</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7161</v>
+        <v>-2.7673</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4772</v>
+        <v>1.8772</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7043</v>
+        <v>2.2756</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7729</v>
+        <v>-0.3984</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4874</v>
+        <v>-5.1115</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4306</v>
+        <v>-2.7427</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0568</v>
+        <v>-2.3688</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8842</v>
+        <v>0.6488</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2126</v>
+        <v>-0.0154</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6715</v>
+        <v>0.6642</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0722</v>
+        <v>3.3584</v>
       </c>
       <c r="W15" t="n">
-        <v>1.214</v>
+        <v>3.8945</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.2862</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6166</v>
+        <v>3.3068</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0486</v>
+        <v>4.9448</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4319</v>
+        <v>-1.638</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.2343</v>
+        <v>0.3705</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4671</v>
+        <v>-0.9579</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.7673</v>
+        <v>1.3284</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8772</v>
+        <v>4.2239</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2756</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3984</v>
+        <v>3.2254</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.1115</v>
+        <v>-3.8534</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.7427</v>
+        <v>-1.9564</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.3688</v>
+        <v>-1.897</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5515</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R16" t="n">
         <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0589</v>
+        <v>-0.2829</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7231</v>
+        <v>-0.6247</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6642</v>
+        <v>0.3418</v>
       </c>
       <c r="V16" t="n">
-        <v>3.3584</v>
+        <v>4.147</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8945</v>
+        <v>4.8249</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5661</v>
+        <v>2.4877</v>
       </c>
       <c r="E17" t="n">
-        <v>4.473</v>
+        <v>2.744</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9069</v>
+        <v>-0.2563</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3705</v>
+        <v>0.9898</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9579</v>
+        <v>0.2736</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3284</v>
+        <v>0.7161</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2239</v>
+        <v>2.4772</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.7043</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2254</v>
+        <v>0.7729</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.8534</v>
+        <v>-1.4874</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9564</v>
+        <v>-1.4306</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.897</v>
+        <v>-0.0568</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0236</v>
+        <v>1.1784</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0965</v>
+        <v>0.2126</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.9658</v>
       </c>
       <c r="V17" t="n">
-        <v>4.147</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>4.8249</v>
+        <v>1.214</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0274</v>
+        <v>-0.3984</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6317</v>
+        <v>-1.1035</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2856</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4722</v>
+        <v>0.1013</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3462</v>
+        <v>-0.1256</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1418</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ACCORSI</t>
+          <t>M. BAIOCCHI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1766</v>
+        <v>-0.4273</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1566</v>
+        <v>-1.4232</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3332</v>
+        <v>0.9959</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4098</v>
+        <v>0.6351</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3841</v>
+        <v>0.9328</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7939</v>
+        <v>-0.2977</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2585</v>
+        <v>1.25</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4703</v>
+        <v>1.1763</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.2118</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6683</v>
+        <v>-0.6148</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0862</v>
+        <v>-0.2435</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5821</v>
+        <v>-0.3713</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4498</v>
+        <v>0.0973</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1019</v>
+        <v>-0.3536</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5518</v>
+        <v>0.4509</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BAIOCCHI</t>
+          <t>M. ACCORSI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8985</v>
+        <v>-0.5812</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6591</v>
+        <v>-0.3152</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7606000000000001</v>
+        <v>-0.266</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6351</v>
+        <v>-0.4098</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9328</v>
+        <v>2.3841</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2977</v>
+        <v>-2.7939</v>
       </c>
       <c r="J20" t="n">
-        <v>1.25</v>
+        <v>0.2585</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1763</v>
+        <v>2.4703</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>-2.2118</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6148</v>
+        <v>-0.6683</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2435</v>
+        <v>-0.0862</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3713</v>
+        <v>-0.5821</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3738</v>
+        <v>0.0452</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5895</v>
+        <v>-0.5737</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2157</v>
+        <v>0.619</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.5905</v>
+        <v>-5.8765</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5159</v>
+        <v>-1.6338</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0746</v>
+        <v>-4.2426</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0407</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2183</v>
+        <v>-0.0677</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2513</v>
+        <v>-0.3692</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4696</v>
+        <v>0.3016</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.008</v>
+        <v>-6.2275</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6853</v>
+        <v>-2.0391</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3228</v>
+        <v>-4.1884</v>
       </c>
       <c r="G22" t="n">
         <v>-5.0675</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0281</v>
+        <v>-0.2475</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1098</v>
+        <v>-0.4637</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.2161</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5856</v>
+        <v>-6.7542</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5117</v>
+        <v>-3.7476</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0738</v>
+        <v>-3.0066</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2548</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1511</v>
+        <v>-0.0176</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3462</v>
+        <v>0.1103</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.195</v>
+        <v>-0.1278</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.9453</v>
+        <v>-9.7094</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.7038</v>
+        <v>-7.4679</v>
       </c>
       <c r="F24" t="n">
         <v>-2.2415</v>
@@ -2326,10 +2326,10 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6642</v>
+        <v>-0.4283</v>
       </c>
       <c r="U24" t="n">
         <v>0.2908</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.8558</v>
+        <v>-20.8557</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.285299999999999</v>
+        <v>-4.2852</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.5704</v>
+        <v>-16.5703</v>
       </c>
       <c r="G25" t="n">
         <v>-21.9982</v>
@@ -2383,7 +2383,7 @@
         <v>7.584299999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.0587</v>
+        <v>-2.058700000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-27.5239</v>
@@ -2395,7 +2395,7 @@
         <v>-12.6468</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.3196</v>
+        <v>-2.319600000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.3964</v>
@@ -2413,13 +2413,13 @@
         <v>3.9493</v>
       </c>
       <c r="V25" t="n">
-        <v>2.1444</v>
+        <v>2.144399999999999</v>
       </c>
       <c r="W25" t="n">
         <v>10.217</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.072600000000001</v>
+        <v>-8.0726</v>
       </c>
     </row>
   </sheetData>
